--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T11:37:47+00:00</t>
+    <t>2026-09-22T11:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$53</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1944" uniqueCount="373">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T11:13:44+00:00</t>
+    <t>2026-09-23T05:33:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -478,7 +478,7 @@
 </t>
   </si>
   <si>
-    <t>Eindeutiger Identifikator für das Arzneimittel. Wird nicht benötigt, da PZN, sofern vorhanden, im Code angegeben wird.</t>
+    <t>Business identifier for this medication</t>
   </si>
   <si>
     <t>Business identifier for this medication.</t>
@@ -500,7 +500,7 @@
 </t>
   </si>
   <si>
-    <t>Code des Arzneimittels. Hier muss die Pharmazentralnummer (PZN) aus der ASP-Liste angegeben werden, sofern vorhanden.</t>
+    <t>Code des Arzneimittels. Hier muss die Pharmazentralnummer (PZN) aus der ASP-Liste angegeben werden.</t>
   </si>
   <si>
     <t>A code (or set of codes) that specify this medication, or a textual description if no code is available. Usage note: This could be a standard medication code such as a code from RxNorm, SNOMED CT, IDMP etc. It could also be a national or local formulary code, optionally with translations to other code systems.</t>
@@ -591,13 +591,6 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:system}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
     <t>CodeableConcept.coding</t>
   </si>
   <si>
@@ -607,27 +600,12 @@
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
-    <t>Medication.code.coding:PZN</t>
-  </si>
-  <si>
-    <t>PZN</t>
-  </si>
-  <si>
-    <t>Medication.code.coding:PZN.id</t>
-  </si>
-  <si>
     <t>Medication.code.coding.id</t>
   </si>
   <si>
-    <t>Medication.code.coding:PZN.extension</t>
-  </si>
-  <si>
     <t>Medication.code.coding.extension</t>
   </si>
   <si>
-    <t>Medication.code.coding:PZN.system</t>
-  </si>
-  <si>
     <t>Medication.code.coding.system</t>
   </si>
   <si>
@@ -655,9 +633,6 @@
     <t>C*E.3</t>
   </si>
   <si>
-    <t>Medication.code.coding:PZN.version</t>
-  </si>
-  <si>
     <t>Medication.code.coding.version</t>
   </si>
   <si>
@@ -679,9 +654,6 @@
     <t>C*E.7</t>
   </si>
   <si>
-    <t>Medication.code.coding:PZN.code</t>
-  </si>
-  <si>
     <t>Medication.code.coding.code</t>
   </si>
   <si>
@@ -703,9 +675,6 @@
     <t>C*E.1</t>
   </si>
   <si>
-    <t>Medication.code.coding:PZN.display</t>
-  </si>
-  <si>
     <t>Medication.code.coding.display</t>
   </si>
   <si>
@@ -725,9 +694,6 @@
   </si>
   <si>
     <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>Medication.code.coding:PZN.userSelected</t>
   </si>
   <si>
     <t>Medication.code.coding.userSelected</t>
@@ -758,36 +724,6 @@
     <t>Sometimes implied by being first</t>
   </si>
   <si>
-    <t>Medication.code.coding:PCID</t>
-  </si>
-  <si>
-    <t>PCID</t>
-  </si>
-  <si>
-    <t>Medication.code.coding:PCID.id</t>
-  </si>
-  <si>
-    <t>Medication.code.coding:PCID.extension</t>
-  </si>
-  <si>
-    <t>Medication.code.coding:PCID.system</t>
-  </si>
-  <si>
-    <t>1.2.40.0.34.4.27</t>
-  </si>
-  <si>
-    <t>Medication.code.coding:PCID.version</t>
-  </si>
-  <si>
-    <t>Medication.code.coding:PCID.code</t>
-  </si>
-  <si>
-    <t>Medication.code.coding:PCID.display</t>
-  </si>
-  <si>
-    <t>Medication.code.coding:PCID.userSelected</t>
-  </si>
-  <si>
     <t>Medication.code.text</t>
   </si>
   <si>
@@ -816,7 +752,7 @@
   </si>
   <si>
     <t>Verfügbarkeitsstatus des Arzneimittels:(req) active | inactive | entered-in-error. https://hl7.org/fhir/R4/valueset-medication-status.html.
- Keine Verwendung im Kontext Planeintrag.</t>
+ Keine Verwendung.</t>
   </si>
   <si>
     <t>A code to indicate if the medication is in active use.</t>
@@ -844,7 +780,7 @@
 </t>
   </si>
   <si>
-    <t>Der Hersteller des Arzneimittels. Keine Verwendung im Kontext Planeintrag.</t>
+    <t>Manufacturer of the item</t>
   </si>
   <si>
     <t>Describes the details of the manufacturer of the medication product.  This is not intended to represent the distributor of a medication product.</t>
@@ -865,7 +801,7 @@
     <t>Medication.form</t>
   </si>
   <si>
-    <t>Die Darreichungsform des Arzneimittels. Wenn PZN vorhanden 0..0, da Anreicherung aus ASP-Liste durch Fachanwendung.</t>
+    <t>Die Darreichungsform des Arzneimittels.</t>
   </si>
   <si>
     <t>Describes the form of the item.  Powder; tablets; capsule.</t>
@@ -874,7 +810,7 @@
     <t>When Medication is referenced from MedicationRequest, this is the ordered form.  When Medication is referenced within MedicationDispense, this is the dispensed form.  When Medication is referenced within MedicationAdministration, this is administered form.</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet-elga-medikationmengenart</t>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-medikationdarreichungsform</t>
   </si>
   <si>
     <t>coding.code =  //element(*,DrugCodedType)/FormCode@@ -895,14 +831,184 @@
 </t>
   </si>
   <si>
-    <t>Die Gesamtmenge des Arzneimittels in der Verpackung. 
-Wenn PZN vorhanden 0..0, da Anreicherung aus ASP-Liste durch Fachanwendung.</t>
+    <t>Die Gesamtmenge des Arzneimittels in der Verpackung.</t>
   </si>
   <si>
     <t>Specific amount of the drug in the packaged product.  For example, when specifying a product that has the same strength (For example, Insulin glargine 100 unit per mL solution for injection), this attribute provides additional clarification of the package amount (For example, 3 mL, 10mL, etc.).</t>
   </si>
   <si>
     <t>.quantity</t>
+  </si>
+  <si>
+    <t>Medication.amount.id</t>
+  </si>
+  <si>
+    <t>Medication.amount.extension</t>
+  </si>
+  <si>
+    <t>Medication.amount.numerator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>Numerator value</t>
+  </si>
+  <si>
+    <t>The value of the numerator.</t>
+  </si>
+  <si>
+    <t>Ratio.numerator</t>
+  </si>
+  <si>
+    <t>.numerator</t>
+  </si>
+  <si>
+    <t>Medication.amount.numerator.id</t>
+  </si>
+  <si>
+    <t>Medication.amount.numerator.extension</t>
+  </si>
+  <si>
+    <t>Medication.amount.numerator.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
+</t>
+  </si>
+  <si>
+    <t>Numerical value (with implicit precision)</t>
+  </si>
+  <si>
+    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
+  </si>
+  <si>
+    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
+  </si>
+  <si>
+    <t>Precision is handled implicitly in almost all cases of measurement.</t>
+  </si>
+  <si>
+    <t>Quantity.value</t>
+  </si>
+  <si>
+    <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
+  </si>
+  <si>
+    <t>SN.2  / CQ - N/A</t>
+  </si>
+  <si>
+    <t>Medication.amount.numerator.comparator</t>
+  </si>
+  <si>
+    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+  </si>
+  <si>
+    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
+  </si>
+  <si>
+    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
+  </si>
+  <si>
+    <t>If there is no comparator, then there is no modification of the value</t>
+  </si>
+  <si>
+    <t>How the Quantity should be understood and represented.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
+  </si>
+  <si>
+    <t>Quantity.comparator</t>
+  </si>
+  <si>
+    <t>IVL properties</t>
+  </si>
+  <si>
+    <t>SN.1  / CQ.1</t>
+  </si>
+  <si>
+    <t>Medication.amount.numerator.unit</t>
+  </si>
+  <si>
+    <t>Unit representation</t>
+  </si>
+  <si>
+    <t>A human-readable form of the unit.</t>
+  </si>
+  <si>
+    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
+  </si>
+  <si>
+    <t>Quantity.unit</t>
+  </si>
+  <si>
+    <t>PQ.unit</t>
+  </si>
+  <si>
+    <t>(see OBX.6 etc.) / CQ.2</t>
+  </si>
+  <si>
+    <t>Medication.amount.numerator.system</t>
+  </si>
+  <si>
+    <t>System that defines coded unit form</t>
+  </si>
+  <si>
+    <t>The identification of the system that provides the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>Need to know the system that defines the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>Quantity.system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qty-3
+</t>
+  </si>
+  <si>
+    <t>CO.codeSystem, PQ.translation.codeSystem</t>
+  </si>
+  <si>
+    <t>Medication.amount.numerator.code</t>
+  </si>
+  <si>
+    <t>Coded form of the unit</t>
+  </si>
+  <si>
+    <t>A computer processable form of the unit in some unit representation system.</t>
+  </si>
+  <si>
+    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
+  </si>
+  <si>
+    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/ValueSet-elga-medikationmengenart</t>
+  </si>
+  <si>
+    <t>Quantity.code</t>
+  </si>
+  <si>
+    <t>PQ.code, MO.currency, PQ.translation.code</t>
+  </si>
+  <si>
+    <t>Medication.amount.denominator</t>
+  </si>
+  <si>
+    <t>Denominator value</t>
+  </si>
+  <si>
+    <t>The value of the denominator.</t>
+  </si>
+  <si>
+    <t>Ratio.denominator</t>
+  </si>
+  <si>
+    <t>.denominator</t>
   </si>
   <si>
     <t>Medication.ingredient</t>
@@ -912,7 +1018,7 @@
 </t>
   </si>
   <si>
-    <t>Wirkstoffe. Keine Angabe, wenn PZN vorhanden (Anreicherung aus ASP-Liste durch Fachanwendung).</t>
+    <t>Wirkstoffe.</t>
   </si>
   <si>
     <t>Identifies a particular constituent of interest in the product.</t>
@@ -951,7 +1057,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-substance-wirkstoff) &lt;&lt;contained&gt;&gt;</t>
+Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-substance-wirkstoff|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation) &lt;&lt;contained&gt;&gt;</t>
   </si>
   <si>
     <t>The actual ingredient or content</t>
@@ -967,6 +1073,9 @@
 </t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>.player</t>
   </si>
   <si>
@@ -985,7 +1094,7 @@
     <t>itemReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-substance-wirkstoff) &lt;&lt;contained&gt;&gt;
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-substance-wirkstoff|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation) &lt;&lt;contained&gt;&gt;
 </t>
   </si>
   <si>
@@ -1397,11 +1506,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN51"/>
+  <dimension ref="A1:AN53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.22265625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="32.79296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="34.52734375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="18.3359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1410,7 +1519,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="90.55859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="168.2734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1425,7 +1534,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="47.4921875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.2578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="55.5546875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -1675,7 +1784,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>86</v>
       </c>
@@ -1688,13 +1797,13 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G3" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>21</v>
@@ -1789,7 +1898,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>94</v>
       </c>
@@ -1808,7 +1917,7 @@
         <v>87</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>21</v>
@@ -1917,7 +2026,7 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
@@ -2129,7 +2238,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
@@ -2148,7 +2257,7 @@
         <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>21</v>
@@ -2603,7 +2712,7 @@
         <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -2701,7 +2810,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>151</v>
       </c>
@@ -2714,13 +2823,13 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>21</v>
@@ -3118,17 +3227,19 @@
         <v>21</v>
       </c>
       <c r="AB15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AC15" s="2"/>
-      <c r="AD15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3146,25 +3257,23 @@
         <v>21</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="16" hidden="true">
+      <c r="A16" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AM15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>186</v>
-      </c>
       <c r="B16" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>21</v>
       </c>
@@ -3176,29 +3285,25 @@
         <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>180</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>21</v>
       </c>
@@ -3246,50 +3351,50 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>185</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
@@ -3301,15 +3406,17 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>21</v>
@@ -3346,31 +3453,31 @@
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>21</v>
+        <v>171</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>21</v>
@@ -3387,21 +3494,21 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>21</v>
@@ -3410,21 +3517,23 @@
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>134</v>
+        <v>187</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>189</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
       </c>
@@ -3433,7 +3542,7 @@
         <v>21</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>21</v>
@@ -3460,51 +3569,51 @@
         <v>21</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>21</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3512,7 +3621,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>87</v>
@@ -3527,20 +3636,18 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>101</v>
+        <v>164</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
       </c>
@@ -3549,7 +3656,7 @@
         <v>21</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>198</v>
+        <v>21</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>21</v>
@@ -3620,7 +3727,7 @@
         <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3628,7 +3735,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>87</v>
@@ -3643,18 +3750,18 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>164</v>
+        <v>107</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" s="2"/>
+      <c r="O20" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="N20" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
       </c>
@@ -3702,7 +3809,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3720,21 +3827,21 @@
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>209</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3742,7 +3849,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>87</v>
@@ -3757,17 +3864,17 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -3816,7 +3923,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3834,21 +3941,21 @@
         <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3871,17 +3978,19 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>164</v>
+        <v>217</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -3930,7 +4039,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3948,21 +4057,21 @@
         <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>225</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3985,19 +4094,19 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -4046,7 +4155,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4064,25 +4173,23 @@
         <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>237</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>21</v>
       </c>
@@ -4091,32 +4198,30 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I24" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>176</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>177</v>
+        <v>234</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>178</v>
+        <v>235</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>180</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
@@ -4140,13 +4245,13 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>21</v>
+        <v>237</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>21</v>
+        <v>238</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4164,13 +4269,13 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>183</v>
+        <v>233</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>21</v>
@@ -4182,21 +4287,21 @@
         <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>184</v>
+        <v>240</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>185</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>189</v>
+        <v>241</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4216,16 +4321,16 @@
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>164</v>
+        <v>242</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>165</v>
+        <v>243</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>166</v>
+        <v>244</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4276,7 +4381,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>167</v>
+        <v>241</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4288,41 +4393,41 @@
         <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>168</v>
+        <v>246</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>21</v>
+        <v>247</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>21</v>
+        <v>248</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>191</v>
+        <v>249</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>21</v>
@@ -4331,16 +4436,16 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>134</v>
+        <v>250</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>170</v>
+        <v>251</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>136</v>
+        <v>252</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4366,63 +4471,61 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>21</v>
+        <v>253</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>174</v>
+        <v>249</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>21</v>
+        <v>254</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>168</v>
+        <v>255</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>21</v>
+        <v>256</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>193</v>
+        <v>257</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4430,13 +4533,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
@@ -4445,20 +4548,16 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>101</v>
+        <v>258</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>194</v>
+        <v>259</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
       </c>
@@ -4467,7 +4566,7 @@
         <v>21</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>241</v>
+        <v>21</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>21</v>
@@ -4506,7 +4605,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>199</v>
+        <v>257</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4524,21 +4623,21 @@
         <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>200</v>
+        <v>261</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>203</v>
+        <v>262</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4558,20 +4657,18 @@
         <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>164</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>204</v>
+        <v>165</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4620,7 +4717,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>207</v>
+        <v>167</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4632,38 +4729,38 @@
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>211</v>
+        <v>263</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
@@ -4672,21 +4769,21 @@
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>212</v>
+        <v>134</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -4722,51 +4819,51 @@
         <v>21</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>21</v>
+        <v>171</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>217</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>219</v>
+        <v>264</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4774,13 +4871,13 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>21</v>
@@ -4789,18 +4886,16 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>164</v>
+        <v>265</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>221</v>
+        <v>267</v>
       </c>
       <c r="N30" s="2"/>
-      <c r="O30" t="s" s="2">
-        <v>222</v>
-      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
@@ -4848,7 +4943,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>223</v>
+        <v>268</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4866,21 +4961,21 @@
         <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>224</v>
+        <v>269</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>225</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>227</v>
+        <v>270</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4900,23 +4995,19 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>228</v>
+        <v>164</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>229</v>
+        <v>165</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -4964,7 +5055,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>233</v>
+        <v>167</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4976,38 +5067,38 @@
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>234</v>
+        <v>168</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>235</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
@@ -5016,23 +5107,21 @@
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>247</v>
+        <v>134</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>248</v>
+        <v>170</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
       </c>
@@ -5068,51 +5157,51 @@
         <v>21</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>21</v>
+        <v>171</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>251</v>
+        <v>174</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>252</v>
+        <v>168</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>253</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5123,30 +5212,32 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>107</v>
+        <v>273</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
@@ -5170,13 +5261,13 @@
         <v>21</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>258</v>
+        <v>21</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>259</v>
+        <v>21</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>260</v>
+        <v>21</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>21</v>
@@ -5194,7 +5285,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5212,21 +5303,21 @@
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>21</v>
+        <v>280</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5237,32 +5328,36 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>263</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+      <c r="O34" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q34" s="2"/>
+      <c r="Q34" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="R34" t="s" s="2">
         <v>21</v>
       </c>
@@ -5282,13 +5377,13 @@
         <v>21</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>21</v>
+        <v>237</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>21</v>
+        <v>286</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>21</v>
+        <v>287</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
@@ -5306,7 +5401,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5321,24 +5416,24 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>266</v>
+        <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>268</v>
+        <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>269</v>
+        <v>290</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5352,27 +5447,27 @@
         <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J35" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K35" t="s" s="2">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
       </c>
@@ -5396,11 +5491,13 @@
         <v>21</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z35" t="s" s="2">
-        <v>274</v>
+        <v>21</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -5418,7 +5515,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5433,24 +5530,24 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>277</v>
+        <v>297</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5464,7 +5561,7 @@
         <v>87</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
@@ -5473,16 +5570,18 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>279</v>
+        <v>101</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
       </c>
@@ -5530,7 +5629,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5539,7 +5638,7 @@
         <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>21</v>
+        <v>303</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>99</v>
@@ -5548,21 +5647,21 @@
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>21</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5570,10 +5669,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>88</v>
@@ -5582,21 +5681,23 @@
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>284</v>
+        <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
       </c>
@@ -5620,13 +5721,11 @@
         <v>21</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>21</v>
+        <v>310</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>21</v>
@@ -5644,13 +5743,13 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>283</v>
+        <v>311</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
@@ -5662,21 +5761,21 @@
         <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>21</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>289</v>
+        <v>313</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>289</v>
+        <v>313</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5687,7 +5786,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>21</v>
@@ -5696,16 +5795,16 @@
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>164</v>
+        <v>265</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>165</v>
+        <v>314</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>166</v>
+        <v>315</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5756,7 +5855,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>167</v>
+        <v>316</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5768,13 +5867,13 @@
         <v>21</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>168</v>
+        <v>317</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>21</v>
@@ -5783,16 +5882,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>290</v>
+        <v>318</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>290</v>
+        <v>318</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5802,7 +5901,7 @@
         <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
@@ -5811,16 +5910,16 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>133</v>
+        <v>319</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>134</v>
+        <v>320</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>170</v>
+        <v>321</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>136</v>
+        <v>322</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5870,7 +5969,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>174</v>
+        <v>318</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5882,13 +5981,13 @@
         <v>21</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>168</v>
+        <v>323</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
@@ -5899,46 +5998,42 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>291</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>291</v>
+        <v>324</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>292</v>
+        <v>21</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>293</v>
+        <v>165</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
       </c>
@@ -5986,25 +6081,25 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>295</v>
+        <v>167</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
@@ -6015,21 +6110,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>296</v>
+        <v>325</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>296</v>
+        <v>325</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -6041,18 +6136,18 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>297</v>
+        <v>133</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>298</v>
+        <v>134</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
       </c>
@@ -6088,84 +6183,86 @@
         <v>21</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="AC41" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>296</v>
+        <v>174</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>302</v>
+        <v>168</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>303</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>21</v>
+        <v>327</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I42" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I42" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J42" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>298</v>
+        <v>328</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O42" t="s" s="2">
-        <v>300</v>
+        <v>142</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -6214,55 +6311,53 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>296</v>
+        <v>330</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>303</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
@@ -6271,17 +6366,17 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>308</v>
+        <v>332</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>309</v>
+        <v>333</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>299</v>
+        <v>334</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>300</v>
+        <v>335</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -6318,19 +6413,17 @@
         <v>21</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>21</v>
+        <v>337</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>296</v>
+        <v>331</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>87</v>
@@ -6348,23 +6441,25 @@
         <v>159</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>302</v>
+        <v>338</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>303</v>
+        <v>339</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>21</v>
       </c>
@@ -6385,17 +6480,17 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>228</v>
+        <v>152</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -6444,10 +6539,10 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>87</v>
@@ -6459,26 +6554,28 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>21</v>
+        <v>339</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>315</v>
+        <v>342</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="D45" t="s" s="2">
         <v>21</v>
       </c>
@@ -6499,16 +6596,18 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>279</v>
+        <v>344</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>316</v>
+        <v>345</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
       </c>
@@ -6556,10 +6655,10 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>87</v>
@@ -6571,24 +6670,24 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>318</v>
+        <v>159</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>282</v>
+        <v>338</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>319</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>320</v>
+        <v>346</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>320</v>
+        <v>346</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6599,10 +6698,10 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
@@ -6611,16 +6710,18 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>284</v>
+        <v>217</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>321</v>
+        <v>347</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>322</v>
+        <v>348</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -6668,7 +6769,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>320</v>
+        <v>346</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6683,10 +6784,10 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>266</v>
+        <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>323</v>
+        <v>350</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
@@ -6695,12 +6796,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6714,7 +6815,7 @@
         <v>87</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>21</v>
@@ -6723,13 +6824,13 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>164</v>
+        <v>258</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>165</v>
+        <v>352</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>166</v>
+        <v>353</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6780,7 +6881,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>167</v>
+        <v>351</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6792,38 +6893,38 @@
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>21</v>
+        <v>354</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>168</v>
+        <v>261</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>21</v>
+        <v>355</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -6835,17 +6936,15 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>133</v>
+        <v>319</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>134</v>
+        <v>357</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -6894,25 +6993,25 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>174</v>
+        <v>356</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>168</v>
+        <v>359</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
@@ -6923,46 +7022,42 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>326</v>
+        <v>360</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>326</v>
+        <v>360</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>292</v>
+        <v>21</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>293</v>
+        <v>165</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7010,25 +7105,25 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>295</v>
+        <v>167</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>21</v>
@@ -7039,21 +7134,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>327</v>
+        <v>361</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>327</v>
+        <v>361</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
@@ -7065,15 +7160,17 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>328</v>
+        <v>134</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>21</v>
@@ -7122,71 +7219,75 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>327</v>
+        <v>174</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>266</v>
+        <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>330</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>331</v>
+        <v>362</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>331</v>
+        <v>362</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>21</v>
+        <v>327</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>332</v>
+        <v>133</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>21</v>
       </c>
@@ -7234,35 +7335,259 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AK51" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>336</v>
+      <c r="AK52" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>372</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN51">
+  <autoFilter ref="A1:AN53">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7272,7 +7597,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI50">
+  <conditionalFormatting sqref="A2:AI52">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T05:33:05+00:00</t>
+    <t>2026-09-23T16:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:50:58+00:00</t>
+    <t>2026-09-23T17:09:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T17:09:41+00:00</t>
+    <t>2026-09-24T11:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>79</v>
@@ -3539,10 +3539,10 @@
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:03:30+00:00</t>
+    <t>2026-09-24T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T15:40:45+00:00</t>
+    <t>2026-09-25T14:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T14:56:10+00:00</t>
+    <t>2026-09-29T10:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:09:39+00:00</t>
+    <t>2026-09-29T10:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:46:32+00:00</t>
+    <t>2026-09-29T11:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:13:32+00:00</t>
+    <t>2026-09-29T15:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:22:43+00:00</t>
+    <t>2026-09-30T17:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T17:01:19+00:00</t>
+    <t>2026-09-30T18:21:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:21:17+00:00</t>
+    <t>2026-10-01T11:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:37:05+00:00</t>
+    <t>2026-10-01T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:47:48+00:00</t>
+    <t>2026-10-01T21:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T21:19:24+00:00</t>
+    <t>2026-10-02T13:24:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:24:17+00:00</t>
+    <t>2026-10-07T12:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:21+00:00</t>
+    <t>2026-10-07T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:43+00:00</t>
+    <t>2026-10-08T06:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T06:44:48+00:00</t>
+    <t>2026-10-08T16:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T16:43:43+00:00</t>
+    <t>2026-10-08T20:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:06:16+00:00</t>
+    <t>2026-10-09T14:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T14:33:13+00:00</t>
+    <t>2026-10-09T16:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T16:18:46+00:00</t>
+    <t>2026-10-12T06:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$65</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1944" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2371" uniqueCount="427">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:12:55+00:00</t>
+    <t>2026-10-12T12:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -297,7 +297,7 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
+    <t>Technische id der Ressource</t>
   </si>
   <si>
     <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
@@ -329,14 +329,191 @@
 </t>
   </si>
   <si>
-    <t>Medication.implicitRules</t>
+    <t>Medication.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Medication.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Medication.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Medication.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Medication.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Medication.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Medication.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>Medication.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Medication.implicitRules</t>
+  </si>
+  <si>
+    <t>Fachliche Begründung: Die Ressource wird nach den Regeln dieses Implementierungsleitfadens interpretiert. Zusätzliche implizite Verarbeitungsregeln werden nicht verwendet.</t>
   </si>
   <si>
     <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
@@ -402,6 +579,59 @@
     <t>Act.text?</t>
   </si>
   <si>
+    <t>Medication.text.id</t>
+  </si>
+  <si>
+    <t>Medication.text.extension</t>
+  </si>
+  <si>
+    <t>Medication.text.status</t>
+  </si>
+  <si>
+    <t>generated | extensions | additional | empty</t>
+  </si>
+  <si>
+    <t>The status of the narrative - whether it's entirely generated (from just the defined data or the extensions too), or whether a human authored it and it may contain additional data.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>The status of a resource narrative.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/narrative-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Narrative.status</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Medication.text.div</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xhtml
+</t>
+  </si>
+  <si>
+    <t>Limited xhtml content</t>
+  </si>
+  <si>
+    <t>The actual narrative content, a stripped down version of XHTML.</t>
+  </si>
+  <si>
+    <t>The contents of the html element are an XHTML fragment containing only the basic html formatting elements described in chapters 7-11 and 15 of the HTML 4.0 standard, &lt;a&gt; elements (either name or href), images and internally contained stylesheets. The XHTML content SHALL NOT contain a head, a body, external stylesheet references, scripts, forms, base/link/xlink, frames, iframes and objects.</t>
+  </si>
+  <si>
+    <t>Narrative.div</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+txt-1:The narrative SHALL contain only the basic html formatting elements and attributes described in chapters 7-11 (except section 4 of chapter 9) and 15 of the HTML 4.0 standard, &lt;a&gt; elements (either name or href), images and internally contained style attributes {htmlChecks()}txt-2:The narrative SHALL have some non-whitespace content {htmlChecks()}</t>
+  </si>
+  <si>
     <t>Medication.contained</t>
   </si>
   <si>
@@ -425,47 +655,22 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Medication.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
     <t>Medication.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Fachliche Begründung: Für den Medikationsplan sind keine zusätzlichen Erweiterungen vorgesehen, die die Bedeutung der Ressource oder ihrer Elemente verändern.</t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -507,9 +712,6 @@
   </si>
   <si>
     <t>Depending on the context of use, the code that was actually selected by the user (prescriber, dispenser, etc.) will have the coding.userSelected set to true.  As described in the coding datatype: "A coding may be marked as a "userSelected" if a user selected the particular coded value in a user interface (e.g. the user selects an item in a pick-list). If a user selected coding exists, it is the preferred choice for performing translations etc. Other codes can only be literal translations to alternative code systems, or codes at a lower level of granularity (e.g. a generic code for a vendor-specific primary one).</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>A coded concept that defines the type of a medication.</t>
@@ -537,46 +739,10 @@
     <t>Medication.code.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Medication.code.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
     <t>Medication.code.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
   </si>
   <si>
     <t>Code defined by a terminology system</t>
@@ -759,9 +925,6 @@
   </si>
   <si>
     <t>This status is intended to identify if the medication in a local system is in active use within a drug database or inventory.  For example, a pharmacy system may create a new drug file record for a compounded product "ABC Hospital Special Cream" with an active status.  At some point in the future, it may be determined that the drug record was created with an error and the status is changed to "entered in error".   This status is not intended to specify if a medication is part of a particular formulary.  It is possible that the drug record may be referenced by multiple formularies or catalogues and each of those entries would have a separate status.</t>
-  </si>
-  <si>
-    <t>required</t>
   </si>
   <si>
     <t>A coded concept defining if the medication is in active use.</t>
@@ -1048,6 +1211,9 @@
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -1506,7 +1672,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN53"/>
+  <dimension ref="A1:AN65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.22265625" customWidth="true" bestFit="true"/>
@@ -1533,7 +1699,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="47.4921875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="55.5546875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -1797,7 +1963,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
         <v>87</v>
@@ -2026,16 +2192,16 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>101</v>
@@ -2046,9 +2212,7 @@
       <c r="M5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>104</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>21</v>
@@ -2097,25 +2261,25 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG5" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH5" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI5" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK5" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL5" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="AG5" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH5" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI5" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ5" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK5" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL5" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>21</v>
@@ -2133,14 +2297,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>21</v>
@@ -2152,16 +2316,16 @@
         <v>21</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2187,49 +2351,49 @@
         <v>21</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>21</v>
@@ -2240,14 +2404,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2263,10 +2427,10 @@
         <v>21</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>118</v>
@@ -2343,53 +2507,53 @@
         <v>21</v>
       </c>
       <c r="AL7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN7" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="AM7" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" hidden="true">
-      <c r="A8" t="s" s="2">
-        <v>123</v>
-      </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2439,25 +2603,25 @@
         <v>21</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>21</v>
@@ -2468,21 +2632,21 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
@@ -2491,19 +2655,19 @@
         <v>21</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2553,25 +2717,25 @@
         <v>21</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>21</v>
@@ -2580,48 +2744,46 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="J10" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>21</v>
       </c>
@@ -2669,7 +2831,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2681,13 +2843,13 @@
         <v>21</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>21</v>
@@ -2698,10 +2860,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2724,16 +2886,16 @@
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2759,13 +2921,13 @@
         <v>21</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>21</v>
+        <v>146</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>21</v>
@@ -2783,7 +2945,7 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2801,21 +2963,21 @@
         <v>21</v>
       </c>
       <c r="AL11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN11" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" hidden="true">
+      <c r="A12" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="AM11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>151</v>
-      </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2823,13 +2985,13 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>21</v>
@@ -2838,16 +3000,16 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N12" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2873,37 +3035,37 @@
         <v>21</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="Y12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>151</v>
-      </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>21</v>
@@ -2912,24 +3074,24 @@
         <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>162</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2940,27 +3102,29 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>21</v>
@@ -3009,7 +3173,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3021,13 +3185,13 @@
         <v>21</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>168</v>
+        <v>21</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>21</v>
@@ -3038,21 +3202,21 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>21</v>
@@ -3064,16 +3228,16 @@
         <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3099,99 +3263,97 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>21</v>
+        <v>167</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AC14" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" hidden="true">
-      <c r="A15" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="L15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>180</v>
-      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>21</v>
       </c>
@@ -3239,13 +3401,13 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>21</v>
@@ -3257,21 +3419,21 @@
         <v>21</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>183</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3294,13 +3456,13 @@
         <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>164</v>
+        <v>101</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>166</v>
+        <v>103</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3351,7 +3513,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>167</v>
+        <v>104</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3369,7 +3531,7 @@
         <v>21</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>168</v>
+        <v>105</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>21</v>
@@ -3380,14 +3542,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3406,16 +3568,16 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3453,19 +3615,19 @@
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>171</v>
+        <v>112</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>172</v>
+        <v>113</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>174</v>
+        <v>115</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3477,13 +3639,13 @@
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>168</v>
+        <v>105</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>21</v>
@@ -3492,12 +3654,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3505,41 +3667,37 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>190</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>21</v>
@@ -3557,13 +3715,13 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>21</v>
+        <v>186</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -3581,10 +3739,10 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>87</v>
@@ -3599,21 +3757,21 @@
         <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>194</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3621,31 +3779,31 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3695,10 +3853,10 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>87</v>
@@ -3707,38 +3865,38 @@
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>195</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>21</v>
+        <v>197</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -3747,21 +3905,21 @@
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>107</v>
+        <v>198</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
       </c>
@@ -3809,50 +3967,50 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>208</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -3861,21 +4019,21 @@
         <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>164</v>
+        <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>210</v>
+        <v>109</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
       </c>
@@ -3923,39 +4081,39 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>215</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3966,32 +4124,28 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>217</v>
+        <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
       </c>
@@ -4039,39 +4193,39 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>223</v>
+        <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>224</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4082,7 +4236,7 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>21</v>
@@ -4094,20 +4248,18 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>164</v>
+        <v>211</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
       </c>
@@ -4155,13 +4307,13 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>21</v>
@@ -4173,21 +4325,21 @@
         <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>21</v>
+        <v>216</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>232</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4195,31 +4347,31 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>107</v>
+        <v>218</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4245,13 +4397,13 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>237</v>
+        <v>153</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4269,7 +4421,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4284,24 +4436,24 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>21</v>
+        <v>224</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>21</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4321,16 +4473,16 @@
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>242</v>
+        <v>101</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>243</v>
+        <v>102</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>244</v>
+        <v>103</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4381,7 +4533,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>241</v>
+        <v>104</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4393,41 +4545,41 @@
         <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>245</v>
+        <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>246</v>
+        <v>105</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>247</v>
+        <v>21</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>248</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>21</v>
@@ -4436,16 +4588,16 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>250</v>
+        <v>109</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>251</v>
+        <v>110</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>252</v>
+        <v>111</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4471,61 +4623,63 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>253</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>249</v>
+        <v>115</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>254</v>
+        <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>255</v>
+        <v>105</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>256</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4533,13 +4687,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
@@ -4548,16 +4702,20 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>258</v>
+        <v>141</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>21</v>
       </c>
@@ -4605,13 +4763,13 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>21</v>
@@ -4623,21 +4781,21 @@
         <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>21</v>
+        <v>237</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4660,13 +4818,13 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>164</v>
+        <v>101</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>166</v>
+        <v>103</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4717,7 +4875,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>167</v>
+        <v>104</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4735,7 +4893,7 @@
         <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>168</v>
+        <v>105</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>21</v>
@@ -4746,14 +4904,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>263</v>
+        <v>239</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>263</v>
+        <v>239</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4772,16 +4930,16 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4819,19 +4977,19 @@
         <v>21</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>171</v>
+        <v>112</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>172</v>
+        <v>113</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>174</v>
+        <v>115</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4843,13 +5001,13 @@
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>168</v>
+        <v>105</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>21</v>
@@ -4858,12 +5016,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4871,13 +5029,13 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>21</v>
@@ -4886,22 +5044,26 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>265</v>
+        <v>129</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>21</v>
@@ -4943,7 +5105,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4961,21 +5123,21 @@
         <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>21</v>
+        <v>248</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4995,18 +5157,20 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>164</v>
+        <v>101</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>165</v>
+        <v>250</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5055,7 +5219,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>167</v>
+        <v>253</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5067,38 +5231,38 @@
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>168</v>
+        <v>254</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>21</v>
+        <v>255</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
@@ -5107,21 +5271,21 @@
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>134</v>
+        <v>257</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
       </c>
@@ -5157,51 +5321,51 @@
         <v>21</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>174</v>
+        <v>260</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>168</v>
+        <v>261</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>21</v>
+        <v>262</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5224,19 +5388,17 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>273</v>
+        <v>101</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -5285,7 +5447,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5303,21 +5465,21 @@
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>280</v>
+        <v>269</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5334,30 +5496,30 @@
         <v>21</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>271</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="O34" t="s" s="2">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q34" t="s" s="2">
-        <v>285</v>
-      </c>
+      <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
         <v>21</v>
       </c>
@@ -5377,13 +5539,13 @@
         <v>21</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>237</v>
+        <v>21</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>286</v>
+        <v>21</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>287</v>
+        <v>21</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
@@ -5401,7 +5563,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5419,21 +5581,21 @@
         <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>290</v>
+        <v>278</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5456,17 +5618,19 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>164</v>
+        <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="O35" t="s" s="2">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -5515,7 +5679,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5533,21 +5697,21 @@
         <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>297</v>
+        <v>286</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5558,30 +5722,30 @@
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
       </c>
@@ -5605,13 +5769,13 @@
         <v>21</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>21</v>
+        <v>291</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>21</v>
+        <v>292</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>21</v>
@@ -5629,7 +5793,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5638,7 +5802,7 @@
         <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>303</v>
+        <v>21</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>99</v>
@@ -5647,21 +5811,21 @@
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>297</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5669,13 +5833,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
@@ -5684,20 +5848,16 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>107</v>
+        <v>295</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
       </c>
@@ -5721,11 +5881,13 @@
         <v>21</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="Y37" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z37" t="s" s="2">
-        <v>310</v>
+        <v>21</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>21</v>
@@ -5743,7 +5905,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5758,24 +5920,24 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>21</v>
+        <v>298</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>21</v>
+        <v>300</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5786,27 +5948,29 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -5831,13 +5995,11 @@
         <v>21</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>21</v>
+        <v>306</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -5855,7 +6017,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5870,24 +6032,24 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>21</v>
+        <v>307</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>21</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5898,7 +6060,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>88</v>
@@ -5907,20 +6069,18 @@
         <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -5969,13 +6129,13 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
@@ -5987,7 +6147,7 @@
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
@@ -5998,10 +6158,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6024,13 +6184,13 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>164</v>
+        <v>101</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>166</v>
+        <v>103</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6081,7 +6241,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>167</v>
+        <v>104</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6099,7 +6259,7 @@
         <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>168</v>
+        <v>105</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
@@ -6110,14 +6270,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6136,16 +6296,16 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6183,19 +6343,19 @@
         <v>21</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>174</v>
+        <v>115</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6207,13 +6367,13 @@
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>168</v>
+        <v>105</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
@@ -6222,48 +6382,44 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>327</v>
+        <v>21</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>133</v>
+        <v>318</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6311,25 +6467,25 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>130</v>
+        <v>322</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
@@ -6340,10 +6496,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6351,7 +6507,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>87</v>
@@ -6366,18 +6522,16 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>332</v>
+        <v>101</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>333</v>
+        <v>102</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>334</v>
+        <v>103</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>335</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
       </c>
@@ -6413,20 +6567,22 @@
         <v>21</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AC43" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>337</v>
+        <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>331</v>
+        <v>104</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>87</v>
@@ -6435,43 +6591,41 @@
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>338</v>
+        <v>105</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>339</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>340</v>
+        <v>324</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
@@ -6480,18 +6634,18 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>333</v>
+        <v>109</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
       </c>
@@ -6527,55 +6681,53 @@
         <v>21</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>331</v>
+        <v>115</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>338</v>
+        <v>105</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>339</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>21</v>
       </c>
@@ -6587,26 +6739,28 @@
         <v>87</v>
       </c>
       <c r="H45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J45" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K45" t="s" s="2">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="O45" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -6658,7 +6812,7 @@
         <v>331</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>87</v>
@@ -6670,24 +6824,24 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6701,31 +6855,33 @@
         <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I46" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I46" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J46" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>217</v>
+        <v>163</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q46" s="2"/>
+      <c r="Q46" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="R46" t="s" s="2">
         <v>21</v>
       </c>
@@ -6745,13 +6901,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>21</v>
+        <v>339</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>21</v>
+        <v>340</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -6769,7 +6925,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6787,21 +6943,21 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>21</v>
+        <v>343</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6815,25 +6971,27 @@
         <v>87</v>
       </c>
       <c r="H47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J47" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K47" t="s" s="2">
-        <v>258</v>
+        <v>101</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -6881,7 +7039,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6896,24 +7054,24 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>354</v>
+        <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>261</v>
+        <v>349</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6924,7 +7082,7 @@
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -6933,19 +7091,21 @@
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>319</v>
+        <v>129</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
       </c>
@@ -6993,39 +7153,39 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI48" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>245</v>
+        <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>21</v>
+        <v>350</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7033,31 +7193,35 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>165</v>
+        <v>359</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7081,13 +7245,11 @@
         <v>21</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>21</v>
@@ -7105,7 +7267,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>167</v>
+        <v>364</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7117,38 +7279,38 @@
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>168</v>
+        <v>365</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>21</v>
+        <v>350</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
@@ -7157,20 +7319,18 @@
         <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>133</v>
+        <v>318</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>134</v>
+        <v>367</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>21</v>
@@ -7219,25 +7379,25 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>174</v>
+        <v>369</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>168</v>
+        <v>370</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>21</v>
@@ -7246,16 +7406,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>327</v>
+        <v>21</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7265,29 +7425,27 @@
         <v>79</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>133</v>
+        <v>372</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>329</v>
+        <v>374</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
       </c>
@@ -7335,7 +7493,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>330</v>
+        <v>371</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7347,13 +7505,13 @@
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>130</v>
+        <v>376</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
@@ -7364,10 +7522,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7390,13 +7548,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>164</v>
+        <v>101</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>364</v>
+        <v>102</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>365</v>
+        <v>103</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7447,7 +7605,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>363</v>
+        <v>104</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7459,38 +7617,38 @@
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>245</v>
+        <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>149</v>
+        <v>105</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>366</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -7502,15 +7660,17 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>368</v>
+        <v>108</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>369</v>
+        <v>109</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -7559,35 +7719,1399 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>367</v>
+        <v>115</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="P54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AC55" s="2"/>
+      <c r="AD55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AK53" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AK55" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="D56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="D57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K60" t="s" s="2">
         <v>372</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>426</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN53">
+  <autoFilter ref="A1:AN65">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7597,7 +9121,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI52">
+  <conditionalFormatting sqref="A2:AI64">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4690,7 +4690,7 @@
         <v>87</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1223,7 +1223,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-substance-wirkstoff|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation) &lt;&lt;contained&gt;&gt;</t>
+Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation) &lt;&lt;contained&gt;&gt;</t>
   </si>
   <si>
     <t>The actual ingredient or content</t>
@@ -1260,7 +1260,7 @@
     <t>itemReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-substance-wirkstoff|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation) &lt;&lt;contained&gt;&gt;
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation) &lt;&lt;contained&gt;&gt;
 </t>
   </si>
   <si>
@@ -1685,7 +1685,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="168.2734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="100.89453125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T19:55:22+00:00</t>
+    <t>2026-10-18T08:01:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T09:33:28+00:00</t>
+    <t>2026-10-18T20:24:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$83</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2371" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3022" uniqueCount="451">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1222,11 +1222,7 @@
     <t>Medication.ingredient.item[x]</t>
   </si>
   <si>
-    <t>CodeableConcept
-Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation) &lt;&lt;contained&gt;&gt;</t>
-  </si>
-  <si>
-    <t>The actual ingredient or content</t>
+    <t>Inhaltsstoff codiert. Wirkstoff-Codes stammen aus der ATC-Klassifikation (Anatomical Therapeutic Chemical Classification), die von der WHO herausgegeben wird. Weitere Codes, wie auch die deutsche Bezeichnung der Codes, entsprechen dem GKV-Arzneimittelindex im Wissenschaftlichen Institut der AOK (WidO), AOK Bundesverband GbR, Deutschland, welcher auf den WHO ATC basiert. Zusätzlich kommen ergänzende Codes aus dem Arzneimittelverzeichnis der AGES zum Einsatz.</t>
   </si>
   <si>
     <t>The actual ingredient - either a substance (simple ingredient) or another medication of a medication.</t>
@@ -1235,36 +1231,110 @@
     <t>The ingredient may reference a substance (for example, amoxicillin) or another medication (for example in the case of a compounded product, Glaxal Base).</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
+    <t>.player</t>
+  </si>
+  <si>
+    <t>RXC-2-Component Code  if medication: RXO-1-Requested Give Code / RXE-2-Give Code / RXD-2-Dispense/Give Code / RXG-4-Give Code / RXA-5-Administered Code</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
 </t>
   </si>
   <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>.player</t>
-  </si>
-  <si>
-    <t>RXC-2-Component Code  if medication: RXO-1-Requested Give Code / RXE-2-Give Code / RXD-2-Dispense/Give Code / RXG-4-Give Code / RXA-5-Administered Code</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept</t>
-  </si>
-  <si>
-    <t>itemCodeableConcept</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemReference</t>
-  </si>
-  <si>
-    <t>itemReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation) &lt;&lt;contained&gt;&gt;
-</t>
-  </si>
-  <si>
-    <t>Referenz auf Ressourcen Substance im Fall von magistraler Anwendung.</t>
+    <t>Medication.ingredient.item[x].coding:ATCWidO</t>
+  </si>
+  <si>
+    <t>ATCWidO</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/AtElgaEmedValueSetATC</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:ATCWidO.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:ATCWidO.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:ATCWidO.system</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.system</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:ATCWidO.version</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.version</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:ATCWidO.code</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.code</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:ATCWidO.display</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.display</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:ATCWidO.userSelected</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:WirkstoffeAges</t>
+  </si>
+  <si>
+    <t>WirkstoffeAges</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-wirkstoffe-ages</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:WirkstoffeAges.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:WirkstoffeAges.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:WirkstoffeAges.system</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:WirkstoffeAges.version</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:WirkstoffeAges.code</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:WirkstoffeAges.display</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:WirkstoffeAges.userSelected</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].text</t>
+  </si>
+  <si>
+    <t>Fachliche Begründung: TODO</t>
   </si>
   <si>
     <t>Medication.ingredient.isActive</t>
@@ -1672,12 +1742,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN65"/>
+  <dimension ref="A1:AN83"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.22265625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="34.52734375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="18.3359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="53.15625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.75" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.7734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1685,7 +1755,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="100.89453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="29.08984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2402,7 +2472,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>117</v>
       </c>
@@ -2421,7 +2491,7 @@
         <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>21</v>
@@ -2516,7 +2586,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>122</v>
       </c>
@@ -2535,7 +2605,7 @@
         <v>87</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>21</v>
@@ -7862,7 +7932,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>385</v>
       </c>
@@ -7881,7 +7951,7 @@
         <v>87</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>21</v>
@@ -7890,17 +7960,17 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -7937,14 +8007,16 @@
         <v>21</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AC55" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>391</v>
+        <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>385</v>
@@ -7965,25 +8037,23 @@
         <v>224</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>21</v>
       </c>
@@ -7995,7 +8065,7 @@
         <v>87</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>21</v>
@@ -8004,18 +8074,16 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>218</v>
+        <v>101</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>387</v>
+        <v>102</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>388</v>
+        <v>103</v>
       </c>
       <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>389</v>
-      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8063,10 +8131,10 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>385</v>
+        <v>104</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>87</v>
@@ -8075,43 +8143,41 @@
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>224</v>
+        <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AM56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>396</v>
-      </c>
       <c r="B57" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>397</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>21</v>
@@ -8120,18 +8186,18 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>398</v>
+        <v>108</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>399</v>
+        <v>109</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" t="s" s="2">
-        <v>389</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8167,51 +8233,51 @@
         <v>21</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>385</v>
+        <v>115</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>224</v>
+        <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>392</v>
+        <v>105</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN57" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
         <v>393</v>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>400</v>
-      </c>
       <c r="B58" t="s" s="2">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8222,29 +8288,31 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K58" t="s" s="2">
-        <v>271</v>
+        <v>141</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>401</v>
+        <v>231</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="O58" t="s" s="2">
-        <v>403</v>
+        <v>234</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -8281,25 +8349,23 @@
         <v>21</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>400</v>
+        <v>235</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
@@ -8311,23 +8377,25 @@
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>404</v>
+        <v>236</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>21</v>
+        <v>237</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>21</v>
       </c>
@@ -8345,19 +8413,23 @@
         <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>311</v>
+        <v>141</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>406</v>
+        <v>231</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -8381,13 +8453,11 @@
         <v>21</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>21</v>
+        <v>397</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>21</v>
@@ -8405,13 +8475,13 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>405</v>
+        <v>235</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
@@ -8420,24 +8490,24 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>408</v>
+        <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>314</v>
+        <v>236</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>409</v>
+        <v>237</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8448,7 +8518,7 @@
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>21</v>
@@ -8460,13 +8530,13 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>372</v>
+        <v>101</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>411</v>
+        <v>102</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>412</v>
+        <v>103</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8517,7 +8587,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>410</v>
+        <v>104</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8529,13 +8599,13 @@
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>298</v>
+        <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>413</v>
+        <v>105</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>21</v>
@@ -8546,21 +8616,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -8572,15 +8642,17 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -8617,31 +8689,31 @@
         <v>21</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>21</v>
@@ -8656,46 +8728,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>109</v>
+        <v>241</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>110</v>
+        <v>242</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -8743,75 +8817,73 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>115</v>
+        <v>246</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>105</v>
+        <v>247</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>21</v>
+        <v>248</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>380</v>
+        <v>21</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>381</v>
+        <v>250</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>382</v>
+        <v>251</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -8859,39 +8931,39 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>384</v>
+        <v>253</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>188</v>
+        <v>254</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>21</v>
+        <v>255</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8899,31 +8971,33 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>418</v>
+        <v>257</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>419</v>
+        <v>258</v>
       </c>
       <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>21</v>
       </c>
@@ -8971,7 +9045,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>417</v>
+        <v>260</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8986,24 +9060,24 @@
         <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>298</v>
+        <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>215</v>
+        <v>261</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>420</v>
+        <v>262</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9023,19 +9097,21 @@
         <v>21</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>422</v>
+        <v>101</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>423</v>
+        <v>264</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>424</v>
+        <v>265</v>
       </c>
       <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9083,7 +9159,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>421</v>
+        <v>267</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9098,20 +9174,2072 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="D67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y67" s="2"/>
+      <c r="Z67" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK78" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AL65" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>426</v>
+      <c r="AL78" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="P81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>450</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN65">
+  <autoFilter ref="A1:AN83">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9121,7 +11249,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI64">
+  <conditionalFormatting sqref="A2:AI82">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>79</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3022" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3024" uniqueCount="451">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1150,7 +1150,7 @@
     <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet-elga-medikationmengenart</t>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-medikationmengenart</t>
   </si>
   <si>
     <t>Quantity.code</t>
@@ -1246,7 +1246,7 @@
     <t>Medication.ingredient.item[x].coding</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
+    <t xml:space="preserve">value:system}
 </t>
   </si>
   <si>
@@ -1256,9 +1256,6 @@
     <t>ATCWidO</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/AtElgaEmedValueSetATC</t>
-  </si>
-  <si>
     <t>Medication.ingredient.item[x].coding:ATCWidO.id</t>
   </si>
   <si>
@@ -1277,6 +1274,9 @@
     <t>Medication.ingredient.item[x].coding.system</t>
   </si>
   <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/atc-deutsch-wido</t>
+  </si>
+  <si>
     <t>Medication.ingredient.item[x].coding:ATCWidO.version</t>
   </si>
   <si>
@@ -1307,9 +1307,6 @@
     <t>WirkstoffeAges</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet/elga-wirkstoffe-ages</t>
-  </si>
-  <si>
     <t>Medication.ingredient.item[x].coding:WirkstoffeAges.id</t>
   </si>
   <si>
@@ -1317,6 +1314,9 @@
   </si>
   <si>
     <t>Medication.ingredient.item[x].coding:WirkstoffeAges.system</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/medikation-ages-wirkstoffe</t>
   </si>
   <si>
     <t>Medication.ingredient.item[x].coding:WirkstoffeAges.version</t>
@@ -8453,11 +8453,13 @@
         <v>21</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y59" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z59" t="s" s="2">
-        <v>397</v>
+        <v>21</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>21</v>
@@ -8504,10 +8506,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8616,10 +8618,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8730,10 +8732,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8778,7 +8780,7 @@
         <v>21</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>21</v>
+        <v>403</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>21</v>
@@ -9369,11 +9371,13 @@
         <v>21</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y67" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z67" t="s" s="2">
-        <v>414</v>
+        <v>21</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>21</v>
@@ -9420,10 +9424,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9532,10 +9536,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9646,10 +9650,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9694,7 +9698,7 @@
         <v>21</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>21</v>
+        <v>417</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -588,7 +588,7 @@
     <t>Medication.text.status</t>
   </si>
   <si>
-    <t>generated | extensions | additional | empty</t>
+    <t>Siehe Notes - "Regeln für den Inhalt der narrativen Teile in den Notes".</t>
   </si>
   <si>
     <t>The status of the narrative - whether it's entirely generated (from just the defined data or the extensions too), or whether a human authored it and it may contain additional data.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>AT ELGA e-Medikation Medication Medikation</t>
+    <t>AT ELGA e-Medikation Medication Profil für die Standardmedikation mit PZN</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$90</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3024" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3277" uniqueCount="458">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1172,6 +1172,27 @@
   </si>
   <si>
     <t>.denominator</t>
+  </si>
+  <si>
+    <t>Medication.amount.denominator.id</t>
+  </si>
+  <si>
+    <t>Medication.amount.denominator.extension</t>
+  </si>
+  <si>
+    <t>Medication.amount.denominator.value</t>
+  </si>
+  <si>
+    <t>Medication.amount.denominator.comparator</t>
+  </si>
+  <si>
+    <t>Medication.amount.denominator.unit</t>
+  </si>
+  <si>
+    <t>Medication.amount.denominator.system</t>
+  </si>
+  <si>
+    <t>Medication.amount.denominator.code</t>
   </si>
   <si>
     <t>Medication.ingredient</t>
@@ -1742,7 +1763,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN83"/>
+  <dimension ref="A1:AN90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.15625" customWidth="true" bestFit="true"/>
@@ -7364,7 +7385,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>366</v>
       </c>
@@ -7377,13 +7398,13 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
@@ -7476,7 +7497,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>371</v>
       </c>
@@ -7489,13 +7510,13 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>21</v>
@@ -7504,17 +7525,15 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>372</v>
+        <v>101</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>373</v>
+        <v>102</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -7563,25 +7582,25 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>371</v>
+        <v>104</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>376</v>
+        <v>105</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
@@ -7592,21 +7611,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -7618,15 +7637,17 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -7663,31 +7684,31 @@
         <v>21</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>21</v>
@@ -7702,46 +7723,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>108</v>
+        <v>326</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>109</v>
+        <v>327</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>110</v>
+        <v>328</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -7789,50 +7812,50 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>115</v>
+        <v>331</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>105</v>
+        <v>332</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>21</v>
+        <v>333</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>380</v>
+        <v>21</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
@@ -7844,24 +7867,24 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>381</v>
+        <v>335</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>383</v>
+        <v>337</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q54" s="2"/>
+      <c r="Q54" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="R54" t="s" s="2">
         <v>21</v>
       </c>
@@ -7881,13 +7904,13 @@
         <v>21</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>21</v>
+        <v>339</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>21</v>
+        <v>340</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -7905,39 +7928,39 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>384</v>
+        <v>341</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>188</v>
+        <v>342</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>21</v>
+        <v>343</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7945,32 +7968,32 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J55" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K55" t="s" s="2">
-        <v>218</v>
+        <v>101</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>386</v>
+        <v>345</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>387</v>
+        <v>346</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>388</v>
+        <v>347</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -8019,10 +8042,10 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>385</v>
+        <v>348</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>87</v>
@@ -8034,24 +8057,24 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>224</v>
+        <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>389</v>
+        <v>349</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>390</v>
+        <v>350</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8071,19 +8094,21 @@
         <v>21</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>102</v>
+        <v>352</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>103</v>
+        <v>353</v>
       </c>
       <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+      <c r="O56" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8131,7 +8156,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>104</v>
+        <v>355</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8140,64 +8165,66 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>21</v>
+        <v>356</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>105</v>
+        <v>357</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>21</v>
+        <v>350</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>109</v>
+        <v>359</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>110</v>
+        <v>360</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8221,63 +8248,61 @@
         <v>21</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>115</v>
+        <v>364</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>105</v>
+        <v>365</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>21</v>
+        <v>350</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8285,35 +8310,33 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>141</v>
+        <v>379</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>231</v>
+        <v>380</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>232</v>
+        <v>381</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -8349,17 +8372,19 @@
         <v>21</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AC58" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>235</v>
+        <v>378</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8377,25 +8402,23 @@
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>236</v>
+        <v>383</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>237</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>396</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>21</v>
       </c>
@@ -8407,29 +8430,25 @@
         <v>87</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>231</v>
+        <v>102</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -8477,50 +8496,50 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>235</v>
+        <v>104</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>236</v>
+        <v>105</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>237</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>21</v>
@@ -8532,15 +8551,17 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -8589,19 +8610,19 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>21</v>
@@ -8618,14 +8639,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>107</v>
+        <v>387</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8638,24 +8659,26 @@
         <v>21</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>109</v>
+        <v>388</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>110</v>
+        <v>389</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="O61" s="2"/>
+      <c r="O61" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
       </c>
@@ -8691,19 +8714,19 @@
         <v>21</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>115</v>
+        <v>391</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8721,7 +8744,7 @@
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>105</v>
+        <v>188</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>21</v>
@@ -8732,10 +8755,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8755,22 +8778,20 @@
         <v>21</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>129</v>
+        <v>218</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>241</v>
+        <v>393</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>244</v>
+        <v>395</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -8780,7 +8801,7 @@
         <v>21</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>403</v>
+        <v>21</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>21</v>
@@ -8819,10 +8840,10 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>246</v>
+        <v>392</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>87</v>
@@ -8834,24 +8855,24 @@
         <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>21</v>
+        <v>224</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>247</v>
+        <v>396</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>248</v>
+        <v>397</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8871,20 +8892,18 @@
         <v>21</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>250</v>
+        <v>102</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -8933,7 +8952,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8945,61 +8964,61 @@
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>255</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>257</v>
+        <v>109</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
       </c>
@@ -9035,51 +9054,51 @@
         <v>21</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>260</v>
+        <v>115</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>261</v>
+        <v>105</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>262</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9090,7 +9109,7 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
@@ -9102,17 +9121,19 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="O65" t="s" s="2">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>21</v>
@@ -9149,25 +9170,23 @@
         <v>21</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="AC65" s="2"/>
       <c r="AD65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>21</v>
@@ -9179,23 +9198,25 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>269</v>
+        <v>237</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C66" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="D66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9207,7 +9228,7 @@
         <v>87</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>21</v>
@@ -9216,19 +9237,19 @@
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>271</v>
+        <v>141</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>272</v>
+        <v>231</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>273</v>
+        <v>232</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>274</v>
+        <v>233</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>275</v>
+        <v>234</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -9277,13 +9298,13 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>276</v>
+        <v>235</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>21</v>
@@ -9295,25 +9316,23 @@
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>277</v>
+        <v>236</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>278</v>
+        <v>237</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>21</v>
       </c>
@@ -9325,29 +9344,25 @@
         <v>87</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>231</v>
+        <v>102</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
@@ -9395,50 +9410,50 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>235</v>
+        <v>104</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>236</v>
+        <v>105</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>237</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>21</v>
@@ -9450,15 +9465,17 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -9495,31 +9512,31 @@
         <v>21</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>21</v>
@@ -9534,46 +9551,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>109</v>
+        <v>241</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>110</v>
+        <v>242</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
       </c>
@@ -9582,7 +9601,7 @@
         <v>21</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>21</v>
+        <v>410</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>21</v>
@@ -9609,51 +9628,51 @@
         <v>21</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>115</v>
+        <v>246</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>105</v>
+        <v>247</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>21</v>
+        <v>248</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9661,13 +9680,13 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>21</v>
@@ -9676,20 +9695,18 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
       </c>
@@ -9698,7 +9715,7 @@
         <v>21</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>417</v>
+        <v>21</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>21</v>
@@ -9737,7 +9754,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9755,21 +9772,21 @@
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9777,13 +9794,13 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>21</v>
@@ -9792,18 +9809,18 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>21</v>
       </c>
@@ -9851,7 +9868,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9869,21 +9886,21 @@
         <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>255</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9891,13 +9908,13 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>21</v>
@@ -9906,17 +9923,17 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>163</v>
+        <v>101</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>21</v>
@@ -9965,7 +9982,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9983,21 +10000,21 @@
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>262</v>
+        <v>269</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10020,17 +10037,19 @@
         <v>88</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>101</v>
+        <v>271</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="O73" t="s" s="2">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -10079,7 +10098,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10097,23 +10116,25 @@
         <v>21</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>269</v>
+        <v>278</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C74" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="D74" t="s" s="2">
         <v>21</v>
       </c>
@@ -10125,7 +10146,7 @@
         <v>87</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>21</v>
@@ -10134,19 +10155,19 @@
         <v>88</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>271</v>
+        <v>141</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>272</v>
+        <v>231</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>273</v>
+        <v>232</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>274</v>
+        <v>233</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>275</v>
+        <v>234</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10195,13 +10216,13 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>276</v>
+        <v>235</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>21</v>
@@ -10213,21 +10234,21 @@
         <v>21</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>277</v>
+        <v>236</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>278</v>
+        <v>237</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10238,7 +10259,7 @@
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>21</v>
@@ -10247,23 +10268,19 @@
         <v>21</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>423</v>
+        <v>102</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>21</v>
       </c>
@@ -10311,7 +10328,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>284</v>
+        <v>104</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10323,41 +10340,41 @@
         <v>21</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>285</v>
+        <v>105</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>286</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>21</v>
@@ -10366,18 +10383,18 @@
         <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>271</v>
+        <v>108</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>425</v>
+        <v>109</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" t="s" s="2">
-        <v>427</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
@@ -10413,37 +10430,37 @@
         <v>21</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>424</v>
+        <v>115</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>428</v>
+        <v>105</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>21</v>
@@ -10454,10 +10471,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>429</v>
+        <v>409</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10465,7 +10482,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>87</v>
@@ -10477,19 +10494,23 @@
         <v>21</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>311</v>
+        <v>129</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>430</v>
+        <v>241</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>21</v>
       </c>
@@ -10498,7 +10519,7 @@
         <v>21</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>21</v>
+        <v>424</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>21</v>
@@ -10537,7 +10558,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>429</v>
+        <v>246</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10552,24 +10573,24 @@
         <v>99</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>432</v>
+        <v>21</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>314</v>
+        <v>247</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>433</v>
+        <v>248</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>434</v>
+        <v>412</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10580,7 +10601,7 @@
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>21</v>
@@ -10589,18 +10610,20 @@
         <v>21</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>372</v>
+        <v>101</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>435</v>
+        <v>250</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>21</v>
@@ -10649,7 +10672,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>434</v>
+        <v>253</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10664,24 +10687,24 @@
         <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>298</v>
+        <v>21</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>437</v>
+        <v>254</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>21</v>
+        <v>255</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10689,31 +10712,33 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>102</v>
+        <v>257</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>103</v>
+        <v>258</v>
       </c>
       <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
+      <c r="O79" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>21</v>
       </c>
@@ -10761,7 +10786,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>104</v>
+        <v>260</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10773,38 +10798,38 @@
         <v>21</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>105</v>
+        <v>261</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>21</v>
+        <v>262</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>439</v>
+        <v>416</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>21</v>
@@ -10813,21 +10838,21 @@
         <v>21</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>109</v>
+        <v>264</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O80" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>21</v>
       </c>
@@ -10875,74 +10900,74 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>115</v>
+        <v>267</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>105</v>
+        <v>268</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>21</v>
+        <v>269</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>440</v>
+        <v>418</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>380</v>
+        <v>21</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J81" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>108</v>
+        <v>271</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>381</v>
+        <v>272</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>382</v>
+        <v>273</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>111</v>
+        <v>274</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>383</v>
+        <v>275</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -10991,39 +11016,39 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>384</v>
+        <v>276</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>188</v>
+        <v>277</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>21</v>
+        <v>278</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11034,7 +11059,7 @@
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>21</v>
@@ -11043,19 +11068,23 @@
         <v>21</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K82" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>21</v>
       </c>
@@ -11103,7 +11132,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>441</v>
+        <v>284</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11118,24 +11147,24 @@
         <v>99</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>298</v>
+        <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>215</v>
+        <v>285</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>444</v>
+        <v>286</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11149,7 +11178,7 @@
         <v>87</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>21</v>
@@ -11158,16 +11187,18 @@
         <v>21</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>446</v>
+        <v>271</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
+      <c r="O83" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>21</v>
       </c>
@@ -11215,7 +11246,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11230,20 +11261,810 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK85" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AL83" t="s" s="2">
+      <c r="AL85" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AM83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN83" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>450</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>457</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN83">
+  <autoFilter ref="A1:AN90">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11253,7 +12074,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI82">
+  <conditionalFormatting sqref="A2:AI89">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$101</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3277" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3673" uniqueCount="470">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -987,6 +987,39 @@
     <t>RXO-5-Requested Dosage Form / RXE-6-Give Dosage Form / RXD-6-Actual Dosage Form / RXG-8-Give Dosage Form / RXA-8-Administered Dosage Form</t>
   </si>
   <si>
+    <t>Medication.form.id</t>
+  </si>
+  <si>
+    <t>Medication.form.extension</t>
+  </si>
+  <si>
+    <t>Medication.form.coding</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.id</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.extension</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.system</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.version</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.code</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.display</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Medication.form.text</t>
+  </si>
+  <si>
     <t>Medication.amount</t>
   </si>
   <si>
@@ -1223,6 +1256,183 @@
     <t>Medication.ingredient.modifierExtension</t>
   </si>
   <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]</t>
+  </si>
+  <si>
+    <t>Inhaltsstoff codiert. Wirkstoff-Codes stammen aus der ATC-Klassifikation (Anatomical Therapeutic Chemical Classification), die von der WHO herausgegeben wird. Weitere Codes, wie auch die deutsche Bezeichnung der Codes, entsprechen dem GKV-Arzneimittelindex im Wissenschaftlichen Institut der AOK (WidO), AOK Bundesverband GbR, Deutschland, welcher auf den WHO ATC basiert. Zusätzlich kommen ergänzende Codes aus dem Arzneimittelverzeichnis der AGES zum Einsatz.</t>
+  </si>
+  <si>
+    <t>The actual ingredient - either a substance (simple ingredient) or another medication of a medication.</t>
+  </si>
+  <si>
+    <t>The ingredient may reference a substance (for example, amoxicillin) or another medication (for example in the case of a compounded product, Glaxal Base).</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+at-emed-medication-ingredient-atcwido-oder-wirkstoffeages:Der Wirkstoff muss entweder mit einem Code aus ATC (WIdO) oder aus dem AGES-Wirkstoffverzeichnis angegeben werden. {coding.where(system = 'https://termgit.elga.gv.at/CodeSystem/atc-deutsch-wido' or system = 'https://termgit.elga.gv.at/CodeSystem/medikation-ages-wirkstoffe').exists()}</t>
+  </si>
+  <si>
+    <t>.player</t>
+  </si>
+  <si>
+    <t>RXC-2-Component Code  if medication: RXO-1-Requested Give Code / RXE-2-Give Code / RXD-2-Dispense/Give Code / RXG-4-Give Code / RXA-5-Administered Code</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:ATCWidO</t>
+  </si>
+  <si>
+    <t>ATCWidO</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:ATCWidO.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:ATCWidO.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:ATCWidO.system</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.system</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/atc-deutsch-wido</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:ATCWidO.version</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.version</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:ATCWidO.code</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.code</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:ATCWidO.display</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.display</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:ATCWidO.userSelected</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:WirkstoffeAges</t>
+  </si>
+  <si>
+    <t>WirkstoffeAges</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:WirkstoffeAges.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:WirkstoffeAges.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:WirkstoffeAges.system</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/medikation-ages-wirkstoffe</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:WirkstoffeAges.version</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:WirkstoffeAges.code</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:WirkstoffeAges.display</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding:WirkstoffeAges.userSelected</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].text</t>
+  </si>
+  <si>
+    <t>Fachliche Begründung: TODO</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.isActive</t>
+  </si>
+  <si>
+    <t>Aktive Wirkstoff TRUE/FALSE</t>
+  </si>
+  <si>
+    <t>Indication of whether this ingredient affects the therapeutic action of the drug.</t>
+  </si>
+  <si>
+    <t>True indicates that the ingredient affects the therapeutic action of the drug (i.e. active). +False indicates that the ingredient does not affect the therapeutic action of the drug (i.e. inactive).</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.strength</t>
+  </si>
+  <si>
+    <t>Menge der vorhandenen Zutaten.</t>
+  </si>
+  <si>
+    <t>Specifies how many (or how much) of the items there are in this Medication.  For example, 250 mg per tablet.  This is expressed as a ratio where the numerator is 250mg and the denominator is 1 tablet.</t>
+  </si>
+  <si>
+    <t>//element(*,DrugCodedType)/Strength</t>
+  </si>
+  <si>
+    <t>RXC-3-Component Amount &amp; RXC-4-Component Units  if medication: RXO-2-Requested Give Amount - Minimum &amp; RXO-4-Requested Give Units / RXO-3-Requested Give Amount - Maximum &amp; RXO-4-Requested Give Units / RXO-11-Requested Dispense Amount &amp; RXO-12-Requested Dispense Units / RXE-3-Give Amount - Minimum &amp; RXE-5-Give Units / RXE-4-Give Amount - Maximum &amp; RXE-5-Give Units / RXE-10-Dispense Amount &amp; RXE-10-Dispense Units</t>
+  </si>
+  <si>
+    <t>Medication.batch</t>
+  </si>
+  <si>
+    <t>Informationen zur Charge des Arzneimittels.</t>
+  </si>
+  <si>
+    <t>Information that only applies to packages (not products).</t>
+  </si>
+  <si>
+    <t>.player[classCode=CONT]</t>
+  </si>
+  <si>
+    <t>Medication.batch.id</t>
+  </si>
+  <si>
+    <t>Medication.batch.extension</t>
+  </si>
+  <si>
+    <t>Medication.batch.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user contentmodifiers</t>
   </si>
@@ -1235,179 +1445,6 @@
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]</t>
-  </si>
-  <si>
-    <t>Inhaltsstoff codiert. Wirkstoff-Codes stammen aus der ATC-Klassifikation (Anatomical Therapeutic Chemical Classification), die von der WHO herausgegeben wird. Weitere Codes, wie auch die deutsche Bezeichnung der Codes, entsprechen dem GKV-Arzneimittelindex im Wissenschaftlichen Institut der AOK (WidO), AOK Bundesverband GbR, Deutschland, welcher auf den WHO ATC basiert. Zusätzlich kommen ergänzende Codes aus dem Arzneimittelverzeichnis der AGES zum Einsatz.</t>
-  </si>
-  <si>
-    <t>The actual ingredient - either a substance (simple ingredient) or another medication of a medication.</t>
-  </si>
-  <si>
-    <t>The ingredient may reference a substance (for example, amoxicillin) or another medication (for example in the case of a compounded product, Glaxal Base).</t>
-  </si>
-  <si>
-    <t>.player</t>
-  </si>
-  <si>
-    <t>RXC-2-Component Code  if medication: RXO-1-Requested Give Code / RXE-2-Give Code / RXD-2-Dispense/Give Code / RXG-4-Give Code / RXA-5-Administered Code</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].id</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].extension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:system}
-</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding:ATCWidO</t>
-  </si>
-  <si>
-    <t>ATCWidO</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding:ATCWidO.id</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding.id</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding:ATCWidO.extension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding:ATCWidO.system</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding.system</t>
-  </si>
-  <si>
-    <t>https://termgit.elga.gv.at/CodeSystem/atc-deutsch-wido</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding:ATCWidO.version</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding.version</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding:ATCWidO.code</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding.code</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding:ATCWidO.display</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding.display</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding:ATCWidO.userSelected</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding:WirkstoffeAges</t>
-  </si>
-  <si>
-    <t>WirkstoffeAges</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding:WirkstoffeAges.id</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding:WirkstoffeAges.extension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding:WirkstoffeAges.system</t>
-  </si>
-  <si>
-    <t>https://termgit.elga.gv.at/CodeSystem/medikation-ages-wirkstoffe</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding:WirkstoffeAges.version</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding:WirkstoffeAges.code</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding:WirkstoffeAges.display</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding:WirkstoffeAges.userSelected</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].text</t>
-  </si>
-  <si>
-    <t>Fachliche Begründung: TODO</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.isActive</t>
-  </si>
-  <si>
-    <t>Aktive Wirkstoff TRUE/FALSE</t>
-  </si>
-  <si>
-    <t>Indication of whether this ingredient affects the therapeutic action of the drug.</t>
-  </si>
-  <si>
-    <t>True indicates that the ingredient affects the therapeutic action of the drug (i.e. active). -False indicates that the ingredient does not affect the therapeutic action of the drug (i.e. inactive).</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.strength</t>
-  </si>
-  <si>
-    <t>Menge der vorhandenen Zutaten.</t>
-  </si>
-  <si>
-    <t>Specifies how many (or how much) of the items there are in this Medication.  For example, 250 mg per tablet.  This is expressed as a ratio where the numerator is 250mg and the denominator is 1 tablet.</t>
-  </si>
-  <si>
-    <t>//element(*,DrugCodedType)/Strength</t>
-  </si>
-  <si>
-    <t>RXC-3-Component Amount &amp; RXC-4-Component Units  if medication: RXO-2-Requested Give Amount - Minimum &amp; RXO-4-Requested Give Units / RXO-3-Requested Give Amount - Maximum &amp; RXO-4-Requested Give Units / RXO-11-Requested Dispense Amount &amp; RXO-12-Requested Dispense Units / RXE-3-Give Amount - Minimum &amp; RXE-5-Give Units / RXE-4-Give Amount - Maximum &amp; RXE-5-Give Units / RXE-10-Dispense Amount &amp; RXE-10-Dispense Units</t>
-  </si>
-  <si>
-    <t>Medication.batch</t>
-  </si>
-  <si>
-    <t>Informationen zur Charge des Arzneimittels.</t>
-  </si>
-  <si>
-    <t>Information that only applies to packages (not products).</t>
-  </si>
-  <si>
-    <t>.player[classCode=CONT]</t>
-  </si>
-  <si>
-    <t>Medication.batch.id</t>
-  </si>
-  <si>
-    <t>Medication.batch.extension</t>
-  </si>
-  <si>
-    <t>Medication.batch.modifierExtension</t>
   </si>
   <si>
     <t>Medication.batch.lotNumber</t>
@@ -1763,7 +1800,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN90"/>
+  <dimension ref="A1:AN101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.15625" customWidth="true" bestFit="true"/>
@@ -4765,7 +4802,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>230</v>
       </c>
@@ -4784,7 +4821,7 @@
         <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
@@ -5107,7 +5144,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>240</v>
       </c>
@@ -5120,13 +5157,13 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>21</v>
@@ -5223,7 +5260,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>249</v>
       </c>
@@ -5242,7 +5279,7 @@
         <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
@@ -5337,7 +5374,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>256</v>
       </c>
@@ -5356,7 +5393,7 @@
         <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
@@ -5451,7 +5488,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>263</v>
       </c>
@@ -5470,7 +5507,7 @@
         <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
@@ -5697,7 +5734,7 @@
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>21</v>
@@ -6135,7 +6172,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>310</v>
       </c>
@@ -6154,22 +6191,22 @@
         <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>311</v>
+        <v>101</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>312</v>
+        <v>102</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>313</v>
+        <v>103</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6220,7 +6257,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>310</v>
+        <v>104</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6232,13 +6269,13 @@
         <v>21</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>314</v>
+        <v>105</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
@@ -6249,21 +6286,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
@@ -6275,15 +6312,17 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -6320,31 +6359,31 @@
         <v>21</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>21</v>
@@ -6359,46 +6398,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>109</v>
+        <v>231</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>110</v>
+        <v>232</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>21</v>
       </c>
@@ -6434,19 +6475,19 @@
         <v>21</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>115</v>
+        <v>235</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6458,27 +6499,27 @@
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>105</v>
+        <v>236</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>21</v>
+        <v>237</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6486,28 +6527,28 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>318</v>
+        <v>101</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>319</v>
+        <v>102</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>320</v>
+        <v>103</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6558,7 +6599,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>321</v>
+        <v>104</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6570,13 +6611,13 @@
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>322</v>
+        <v>105</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
@@ -6587,21 +6628,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>21</v>
@@ -6613,15 +6654,17 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -6658,31 +6701,31 @@
         <v>21</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>21</v>
@@ -6697,46 +6740,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>109</v>
+        <v>241</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>110</v>
+        <v>242</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
       </c>
@@ -6772,51 +6817,51 @@
         <v>21</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>115</v>
+        <v>246</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>105</v>
+        <v>247</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>21</v>
+        <v>248</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6830,7 +6875,7 @@
         <v>87</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
@@ -6839,20 +6884,18 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>326</v>
+        <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>327</v>
+        <v>250</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>328</v>
+        <v>251</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
       </c>
@@ -6900,7 +6943,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>331</v>
+        <v>253</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6918,21 +6961,21 @@
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>332</v>
+        <v>254</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>333</v>
+        <v>255</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6940,16 +6983,16 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
         <v>88</v>
@@ -6958,21 +7001,19 @@
         <v>163</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>335</v>
+        <v>257</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>336</v>
+        <v>258</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>337</v>
+        <v>259</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q46" t="s" s="2">
-        <v>338</v>
-      </c>
+      <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
         <v>21</v>
       </c>
@@ -6992,13 +7033,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>339</v>
+        <v>21</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>340</v>
+        <v>21</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7016,7 +7057,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>341</v>
+        <v>260</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7034,21 +7075,21 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>342</v>
+        <v>261</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>343</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>344</v>
+        <v>318</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>344</v>
+        <v>318</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7062,7 +7103,7 @@
         <v>87</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>21</v>
@@ -7074,14 +7115,14 @@
         <v>101</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>345</v>
+        <v>264</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>346</v>
+        <v>265</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>347</v>
+        <v>266</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7130,7 +7171,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>348</v>
+        <v>267</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7148,21 +7189,21 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>349</v>
+        <v>268</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>350</v>
+        <v>269</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7185,17 +7226,19 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>129</v>
+        <v>271</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>352</v>
+        <v>272</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>354</v>
+        <v>275</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7244,7 +7287,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>355</v>
+        <v>276</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7253,7 +7296,7 @@
         <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>356</v>
+        <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>99</v>
@@ -7262,21 +7305,21 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>357</v>
+        <v>277</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>350</v>
+        <v>278</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7284,13 +7327,13 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>21</v>
@@ -7299,19 +7342,19 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>163</v>
+        <v>101</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>359</v>
+        <v>280</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>360</v>
+        <v>281</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>361</v>
+        <v>282</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>362</v>
+        <v>283</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>21</v>
@@ -7336,11 +7379,13 @@
         <v>21</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y49" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z49" t="s" s="2">
-        <v>363</v>
+        <v>21</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>21</v>
@@ -7358,7 +7403,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>364</v>
+        <v>284</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7376,21 +7421,21 @@
         <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>365</v>
+        <v>285</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>350</v>
+        <v>286</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>366</v>
+        <v>321</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>366</v>
+        <v>321</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7398,7 +7443,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>87</v>
@@ -7413,13 +7458,13 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>367</v>
+        <v>323</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7470,7 +7515,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>369</v>
+        <v>321</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7488,7 +7533,7 @@
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>370</v>
+        <v>325</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>21</v>
@@ -7499,10 +7544,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>371</v>
+        <v>326</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>371</v>
+        <v>326</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7611,10 +7656,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>372</v>
+        <v>327</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>372</v>
+        <v>327</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7725,10 +7770,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>373</v>
+        <v>328</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>373</v>
+        <v>328</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7751,20 +7796,16 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -7812,7 +7853,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7830,21 +7871,21 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>333</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>374</v>
+        <v>334</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>374</v>
+        <v>334</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7861,30 +7902,26 @@
         <v>21</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>163</v>
+        <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>335</v>
+        <v>102</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>336</v>
+        <v>103</v>
       </c>
       <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>337</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q54" t="s" s="2">
-        <v>338</v>
-      </c>
+      <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
         <v>21</v>
       </c>
@@ -7904,13 +7941,13 @@
         <v>21</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>339</v>
+        <v>21</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>340</v>
+        <v>21</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -7928,7 +7965,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>341</v>
+        <v>104</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7940,38 +7977,38 @@
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>342</v>
+        <v>105</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>343</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>375</v>
+        <v>335</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>375</v>
+        <v>335</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
@@ -7980,21 +8017,21 @@
         <v>21</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>345</v>
+        <v>109</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
       </c>
@@ -8030,51 +8067,51 @@
         <v>21</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>348</v>
+        <v>115</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>349</v>
+        <v>105</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>350</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>376</v>
+        <v>336</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>376</v>
+        <v>336</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8097,17 +8134,19 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>129</v>
+        <v>337</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="O56" t="s" s="2">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -8156,7 +8195,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8165,7 +8204,7 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>356</v>
+        <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>99</v>
@@ -8174,21 +8213,21 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>377</v>
+        <v>345</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>377</v>
+        <v>345</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8199,13 +8238,13 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I57" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>88</v>
@@ -8214,21 +8253,21 @@
         <v>163</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q57" s="2"/>
+      <c r="Q57" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="R57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8250,9 +8289,11 @@
       <c r="X57" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Y57" s="2"/>
+      <c r="Y57" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="Z57" t="s" s="2">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>21</v>
@@ -8270,7 +8311,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8288,21 +8329,21 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>378</v>
+        <v>355</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>378</v>
+        <v>355</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8310,33 +8351,33 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K58" t="s" s="2">
-        <v>379</v>
+        <v>101</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>358</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -8384,13 +8425,13 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>378</v>
+        <v>359</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
@@ -8402,21 +8443,21 @@
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>383</v>
+        <v>360</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>384</v>
+        <v>362</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>384</v>
+        <v>362</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8436,19 +8477,21 @@
         <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>102</v>
+        <v>363</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>103</v>
+        <v>364</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -8496,7 +8539,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>104</v>
+        <v>366</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8505,64 +8548,66 @@
         <v>87</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>21</v>
+        <v>367</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>105</v>
+        <v>368</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>109</v>
+        <v>370</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>110</v>
+        <v>371</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -8586,13 +8631,11 @@
         <v>21</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>21</v>
+        <v>374</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -8610,75 +8653,71 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>105</v>
+        <v>376</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>387</v>
+        <v>21</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J61" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>108</v>
+        <v>329</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>21</v>
       </c>
@@ -8726,25 +8765,25 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>188</v>
+        <v>381</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>21</v>
@@ -8753,12 +8792,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8766,13 +8805,13 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>21</v>
@@ -8781,18 +8820,16 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>218</v>
+        <v>101</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>393</v>
+        <v>102</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>394</v>
+        <v>103</v>
       </c>
       <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>395</v>
-      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -8840,10 +8877,10 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>392</v>
+        <v>104</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>87</v>
@@ -8852,38 +8889,38 @@
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>224</v>
+        <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>396</v>
+        <v>105</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>397</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>21</v>
@@ -8895,15 +8932,17 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -8940,31 +8979,31 @@
         <v>21</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>21</v>
@@ -8979,46 +9018,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>108</v>
+        <v>337</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>109</v>
+        <v>338</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>110</v>
+        <v>339</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>21</v>
       </c>
@@ -9054,51 +9095,51 @@
         <v>21</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>115</v>
+        <v>342</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>105</v>
+        <v>343</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>21</v>
+        <v>344</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9109,36 +9150,36 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>231</v>
+        <v>346</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>234</v>
+        <v>348</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q65" s="2"/>
+      <c r="Q65" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="R65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9158,35 +9199,37 @@
         <v>21</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>21</v>
+        <v>350</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>21</v>
+        <v>351</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AC65" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>235</v>
+        <v>352</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>21</v>
@@ -9198,25 +9241,23 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>236</v>
+        <v>353</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>237</v>
+        <v>354</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9228,7 +9269,7 @@
         <v>87</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>21</v>
@@ -9237,19 +9278,17 @@
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>231</v>
+        <v>356</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>234</v>
+        <v>358</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -9298,13 +9337,13 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>235</v>
+        <v>359</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>21</v>
@@ -9316,21 +9355,21 @@
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>236</v>
+        <v>360</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>237</v>
+        <v>361</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9350,19 +9389,21 @@
         <v>21</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>102</v>
+        <v>363</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>103</v>
+        <v>364</v>
       </c>
       <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+      <c r="O67" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
@@ -9410,7 +9451,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>104</v>
+        <v>366</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9419,64 +9460,66 @@
         <v>87</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>21</v>
+        <v>367</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>105</v>
+        <v>368</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>109</v>
+        <v>370</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>110</v>
+        <v>371</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
       </c>
@@ -9500,63 +9543,61 @@
         <v>21</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>21</v>
+        <v>374</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>105</v>
+        <v>376</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>408</v>
+        <v>389</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>409</v>
+        <v>389</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9567,7 +9608,7 @@
         <v>87</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>88</v>
@@ -9576,23 +9617,21 @@
         <v>21</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>129</v>
+        <v>390</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>241</v>
+        <v>391</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>242</v>
+        <v>392</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>21</v>
       </c>
@@ -9601,7 +9640,7 @@
         <v>21</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>410</v>
+        <v>21</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>21</v>
@@ -9640,13 +9679,13 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>246</v>
+        <v>389</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
@@ -9658,21 +9697,21 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>247</v>
+        <v>394</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>248</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9692,20 +9731,18 @@
         <v>21</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>250</v>
+        <v>102</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -9754,7 +9791,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9766,61 +9803,61 @@
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>255</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>257</v>
+        <v>109</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>21</v>
       </c>
@@ -9868,39 +9905,39 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>260</v>
+        <v>115</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>261</v>
+        <v>105</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>262</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>416</v>
+        <v>397</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9911,30 +9948,28 @@
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J72" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>264</v>
+        <v>207</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>265</v>
+        <v>208</v>
       </c>
       <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>266</v>
-      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>21</v>
       </c>
@@ -9982,39 +10017,39 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>267</v>
+        <v>398</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>268</v>
+        <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>269</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10022,34 +10057,32 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>271</v>
+        <v>218</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>272</v>
+        <v>400</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>275</v>
+        <v>402</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -10098,10 +10131,10 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>276</v>
+        <v>399</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>87</v>
@@ -10110,31 +10143,29 @@
         <v>21</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>99</v>
+        <v>403</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>21</v>
+        <v>224</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>277</v>
+        <v>404</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>278</v>
+        <v>405</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="C74" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>21</v>
       </c>
@@ -10146,29 +10177,25 @@
         <v>87</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>231</v>
+        <v>102</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>21</v>
       </c>
@@ -10216,50 +10243,50 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>235</v>
+        <v>104</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>236</v>
+        <v>105</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>237</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>21</v>
@@ -10271,15 +10298,17 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -10316,31 +10345,31 @@
         <v>21</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>21</v>
@@ -10357,44 +10386,46 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>109</v>
+        <v>231</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>110</v>
+        <v>232</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
@@ -10430,11 +10461,9 @@
         <v>21</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="AC76" s="2"/>
       <c r="AD76" t="s" s="2">
         <v>21</v>
       </c>
@@ -10442,7 +10471,7 @@
         <v>114</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>115</v>
+        <v>235</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10454,35 +10483,37 @@
         <v>21</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>105</v>
+        <v>236</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>21</v>
+        <v>237</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C77" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="D77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>87</v>
@@ -10497,19 +10528,19 @@
         <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>21</v>
@@ -10519,7 +10550,7 @@
         <v>21</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>424</v>
+        <v>21</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>21</v>
@@ -10558,13 +10589,13 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>21</v>
@@ -10576,21 +10607,21 @@
         <v>21</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>248</v>
+        <v>237</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10610,20 +10641,18 @@
         <v>21</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>250</v>
+        <v>102</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>21</v>
@@ -10672,7 +10701,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10684,61 +10713,61 @@
         <v>21</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>255</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>257</v>
+        <v>109</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>21</v>
       </c>
@@ -10774,51 +10803,51 @@
         <v>21</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>260</v>
+        <v>115</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>261</v>
+        <v>105</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>262</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10826,13 +10855,13 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>21</v>
@@ -10841,17 +10870,19 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="O80" t="s" s="2">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>21</v>
@@ -10861,7 +10892,7 @@
         <v>21</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>21</v>
@@ -10900,7 +10931,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10918,21 +10949,21 @@
         <v>21</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>269</v>
+        <v>248</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10946,7 +10977,7 @@
         <v>87</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>21</v>
@@ -10955,20 +10986,18 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>271</v>
+        <v>101</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>21</v>
       </c>
@@ -11016,7 +11045,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>276</v>
+        <v>253</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11034,21 +11063,21 @@
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>278</v>
+        <v>255</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11056,13 +11085,13 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>21</v>
@@ -11071,19 +11100,17 @@
         <v>88</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>430</v>
+        <v>257</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>21</v>
@@ -11132,7 +11159,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11150,21 +11177,21 @@
         <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>286</v>
+        <v>262</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11184,20 +11211,20 @@
         <v>21</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>271</v>
+        <v>101</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>432</v>
+        <v>264</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>433</v>
+        <v>265</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>434</v>
+        <v>266</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>21</v>
@@ -11246,7 +11273,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>431</v>
+        <v>267</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11264,21 +11291,21 @@
         <v>21</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>435</v>
+        <v>268</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>21</v>
+        <v>269</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11292,25 +11319,29 @@
         <v>87</v>
       </c>
       <c r="H84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J84" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K84" t="s" s="2">
-        <v>311</v>
+        <v>271</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>437</v>
+        <v>272</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
       </c>
@@ -11358,7 +11389,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>436</v>
+        <v>276</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11373,26 +11404,28 @@
         <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>439</v>
+        <v>21</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>314</v>
+        <v>277</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>440</v>
+        <v>278</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>441</v>
+        <v>427</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="C85" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="C85" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="D85" t="s" s="2">
         <v>21</v>
       </c>
@@ -11401,28 +11434,32 @@
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>379</v>
+        <v>141</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>442</v>
+        <v>231</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>21</v>
       </c>
@@ -11470,13 +11507,13 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>441</v>
+        <v>235</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>21</v>
@@ -11485,24 +11522,24 @@
         <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>298</v>
+        <v>21</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>444</v>
+        <v>236</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>21</v>
+        <v>237</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>445</v>
+        <v>413</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11611,10 +11648,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>446</v>
+        <v>415</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11684,16 +11721,16 @@
         <v>21</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>115</v>
@@ -11723,47 +11760,47 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>447</v>
+        <v>417</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>387</v>
+        <v>21</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J88" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>388</v>
+        <v>241</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>389</v>
+        <v>242</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>111</v>
+        <v>243</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>390</v>
+        <v>244</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>21</v>
@@ -11773,7 +11810,7 @@
         <v>21</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>21</v>
+        <v>432</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>21</v>
@@ -11812,39 +11849,39 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>391</v>
+        <v>246</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>188</v>
+        <v>247</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>21</v>
+        <v>248</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>448</v>
+        <v>420</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11858,24 +11895,26 @@
         <v>87</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K89" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>449</v>
+        <v>250</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>21</v>
@@ -11924,7 +11963,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>448</v>
+        <v>253</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -11939,24 +11978,24 @@
         <v>99</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>298</v>
+        <v>21</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>451</v>
+        <v>255</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>452</v>
+        <v>422</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11964,31 +12003,33 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>453</v>
+        <v>163</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>454</v>
+        <v>257</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>455</v>
+        <v>258</v>
       </c>
       <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+      <c r="O90" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>21</v>
       </c>
@@ -12036,7 +12077,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>452</v>
+        <v>260</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12051,20 +12092,1270 @@
         <v>99</v>
       </c>
       <c r="AK90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="P92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK96" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AL90" t="s" s="2">
+      <c r="AL96" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="AM90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN90" t="s" s="2">
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>457</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="P99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>469</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN90">
+  <autoFilter ref="A1:AN101">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12074,7 +13365,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI89">
+  <conditionalFormatting sqref="A2:AI100">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3673" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3673" uniqueCount="469">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1376,9 +1376,6 @@
   </si>
   <si>
     <t>Medication.ingredient.item[x].text</t>
-  </si>
-  <si>
-    <t>Fachliche Begründung: TODO</t>
   </si>
   <si>
     <t>Medication.ingredient.isActive</t>
@@ -12365,7 +12362,7 @@
         <v>101</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>438</v>
+        <v>280</v>
       </c>
       <c r="M93" t="s" s="2">
         <v>281</v>
@@ -12452,10 +12449,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12481,14 +12478,14 @@
         <v>271</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>21</v>
@@ -12537,7 +12534,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12555,7 +12552,7 @@
         <v>21</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>21</v>
@@ -12566,10 +12563,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12595,10 +12592,10 @@
         <v>322</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12649,7 +12646,7 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -12664,7 +12661,7 @@
         <v>99</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>325</v>
@@ -12673,15 +12670,15 @@
         <v>21</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12707,10 +12704,10 @@
         <v>390</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -12761,7 +12758,7 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -12779,7 +12776,7 @@
         <v>298</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>21</v>
@@ -12790,10 +12787,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12902,10 +12899,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13016,14 +13013,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -13045,16 +13042,16 @@
         <v>108</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>21</v>
@@ -13132,10 +13129,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13161,10 +13158,10 @@
         <v>101</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13215,7 +13212,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13239,15 +13236,15 @@
         <v>21</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13270,13 +13267,13 @@
         <v>21</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -13327,7 +13324,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -13345,13 +13342,13 @@
         <v>298</v>
       </c>
       <c r="AL101" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN101" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>469</v>
       </c>
     </row>
   </sheetData>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-standard-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
